--- a/data/trans_orig/KC10IN_T-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Clase-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN autopercibido (escala)</t>
+          <t>KIDSCREEN autopercibido (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,8; 65,0</t>
+          <t>58,71; 64,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,84; 64,14</t>
+          <t>57,86; 64,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,04; 63,36</t>
+          <t>59,02; 63,59</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,99; 62,23</t>
+          <t>55,32; 62,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,4; 65,25</t>
+          <t>56,53; 64,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,83; 62,38</t>
+          <t>56,72; 62,5</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,24; 63,52</t>
+          <t>53,86; 62,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54,19; 61,25</t>
+          <t>54,54; 61,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,06; 60,64</t>
+          <t>54,94; 60,49</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,26; 57,86</t>
+          <t>52,07; 57,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,0; 63,46</t>
+          <t>55,16; 63,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,14; 60,26</t>
+          <t>54,0; 60,07</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>54,79; 61,06</t>
+          <t>55,13; 60,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,72; 70,54</t>
+          <t>54,78; 71,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55,59; 67,99</t>
+          <t>55,76; 68,58</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55,23; 61,44</t>
+          <t>55,15; 60,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53,57; 59,83</t>
+          <t>53,67; 60,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54,96; 59,14</t>
+          <t>55,08; 59,38</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>55,17; 58,88</t>
+          <t>55,21; 58,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>57,36; 63,0</t>
+          <t>57,29; 62,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57,01; 60,18</t>
+          <t>56,84; 60,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KC10IN_T-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Clase-trans_orig.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,71; 64,69</t>
+          <t>58,82; 64,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,86; 64,38</t>
+          <t>58,14; 64,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,02; 63,59</t>
+          <t>59,03; 63,48</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,32; 62,97</t>
+          <t>54,96; 62,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,53; 64,46</t>
+          <t>56,89; 65,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,72; 62,5</t>
+          <t>56,91; 62,71</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,86; 62,8</t>
+          <t>54,04; 63,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54,54; 61,31</t>
+          <t>54,15; 60,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54,94; 60,49</t>
+          <t>55,03; 60,47</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,07; 57,99</t>
+          <t>52,12; 58,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,16; 63,88</t>
+          <t>55,19; 63,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,0; 60,07</t>
+          <t>54,03; 60,2</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>55,13; 60,78</t>
+          <t>54,89; 60,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,78; 71,57</t>
+          <t>54,82; 71,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55,76; 68,58</t>
+          <t>55,68; 66,8</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55,15; 60,99</t>
+          <t>55,17; 61,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53,67; 60,26</t>
+          <t>53,57; 59,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55,08; 59,38</t>
+          <t>55,08; 59,31</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>55,21; 58,88</t>
+          <t>54,98; 58,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>57,29; 62,66</t>
+          <t>57,27; 62,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,84; 60,51</t>
+          <t>56,97; 60,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KC10IN_T-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Clase-trans_orig.xlsx
@@ -495,12 +495,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>61,47</t>
+          <t>60,7</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>60,92</t>
+          <t>61,27</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61,16</t>
+          <t>60,95</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,82; 64,86</t>
+          <t>57,57; 64,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,14; 64,83</t>
+          <t>58,59; 64,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,03; 63,48</t>
+          <t>58,85; 63,17</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>58,32</t>
+          <t>59,82</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>59,99</t>
+          <t>58,29</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59,2</t>
+          <t>59,08</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,96; 62,4</t>
+          <t>56,35; 64,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,89; 65,87</t>
+          <t>54,92; 62,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,91; 62,71</t>
+          <t>56,69; 62,19</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>57,68</t>
+          <t>57,33</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>57,22</t>
+          <t>57,51</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57,38</t>
+          <t>57,39</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,04; 63,28</t>
+          <t>54,29; 61,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54,15; 60,76</t>
+          <t>54,18; 63,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,03; 60,47</t>
+          <t>55,05; 60,56</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>54,73</t>
+          <t>58,72</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>58,7</t>
+          <t>56,72</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56,78</t>
+          <t>57,96</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,12; 58,14</t>
+          <t>55,33; 63,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,19; 63,85</t>
+          <t>54,64; 59,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,03; 60,2</t>
+          <t>55,71; 61,44</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>57,57</t>
+          <t>59,62</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60,75</t>
+          <t>57,19</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59,56</t>
+          <t>58,65</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>54,89; 60,75</t>
+          <t>54,5; 68,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,82; 71,93</t>
+          <t>54,52; 60,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55,68; 66,8</t>
+          <t>55,3; 66,01</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>57,71</t>
+          <t>56,2</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>56,41</t>
+          <t>57,75</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57,01</t>
+          <t>56,95</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55,17; 61,13</t>
+          <t>53,42; 59,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53,57; 59,82</t>
+          <t>55,34; 61,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55,08; 59,31</t>
+          <t>54,85; 59,07</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>57,38</t>
+          <t>58,88</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>59,19</t>
+          <t>58,06</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58,4</t>
+          <t>58,53</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>54,98; 58,81</t>
+          <t>57,19; 62,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>57,27; 62,43</t>
+          <t>56,95; 59,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,97; 60,57</t>
+          <t>57,5; 60,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KC10IN_T-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Clase-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -97,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -110,6 +112,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN autopercibido (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN autopercibido (escala) (tasa de respuesta: 29,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -546,149 +551,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>60,7</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>61,27</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>60,95</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>60.69810251346676</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>61.2685788071727</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>60.95220356892587</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>57,57; 64,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>58,59; 64,74</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>58,85; 63,17</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>57.56945510821366</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>58.58758470270003</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>58.84960796727582</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>63.99995352065864</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>64.74497847386186</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>63.17496327403256</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>59,82</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>58,29</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>59,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>56,35; 64,9</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54,92; 62,31</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>56,69; 62,19</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>59.82152244661937</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>58.28819030540846</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>59.08390235677854</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>57,33</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>57,51</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>57,39</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>56.34611983627336</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>54.91896168132441</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>56.69304481381817</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>54,29; 61,68</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>54,18; 63,2</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>55,05; 60,56</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>64.89729841538281</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>62.31317236947842</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>62.18894958254245</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -696,149 +661,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>58,72</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>56,72</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>57,96</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>57.32696024030368</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>57.5091190456736</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>57.39361831899718</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>55,33; 63,37</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>54,64; 59,05</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>55,71; 61,44</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>54.29050064059938</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>54.18247551454024</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>55.05464028228028</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>61.68135250626009</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>63.19714192775304</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>60.55557656975084</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>59,62</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>57,19</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58,65</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>54,5; 68,71</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>54,52; 60,55</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>55,3; 66,01</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>58.7220039068827</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>56.71974883967201</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>57.96314336634223</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>56,2</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>57,75</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>56,95</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>55.32752544395154</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>54.63786904179086</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>55.71352531434864</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>53,42; 59,54</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>55,34; 61,51</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>54,85; 59,07</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>63.37476836685762</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>59.04658649732046</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>61.43875442988391</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -846,47 +771,162 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>58,88</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>58,06</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>58,53</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>59.62052575491073</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>57.19263288805018</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>58.65019621431983</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>57,19; 62,02</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>56,95; 59,41</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>57,5; 60,14</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>54.49924337622369</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>54.5166537886272</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>55.3009582531279</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>68.70568080381567</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>60.55051765170781</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>66.01307954452261</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>56.20425591223282</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>57.75081153510735</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>56.94946875474818</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>53.41575202590147</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>55.34129471380993</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>54.85089718925384</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>59.54487856763939</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>61.50534534105992</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>59.07494904108567</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>58.87634761974704</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>58.0648379815263</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>58.53343993683831</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>57.19336713081245</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>56.95237294469457</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>57.49516800622655</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>62.01624688251226</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>59.40572045365916</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>60.14445141669408</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -894,14 +934,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
